--- a/Luban/Config/Datas/Levels/L29/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L29/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L29 W1/25; N=59; EHP=397.188000; normal:17x29,normal:18x30</t>
+          <t>L29 W1/25; N=59; EHP=1105.279383; normal:17x29,normal:18x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L29 W2/25; N=65; EHP=458.190018; normal:17x33,normal:18x32</t>
+          <t>L29 W2/25; N=65; EHP=1275.033436; normal:17x33,normal:18x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10021556,10021558,10049158,10021556,10021558,10049158,10021556,10021558,10049159,10021556,10021558,10049159,10021556,10021558,10049160,10021556,10021558,10049160,10021556,10021558,10049161,10021556,10021558,10049161,10021556,10021558,10049162,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021556,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557</t>
+          <t>10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021558,10021556,10021556,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557,10021557</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L29 W3/25; N=71; EHP=554.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x1,normal:17x21,normal:18x22,swarm:84x19</t>
+          <t>L29 W3/25; N=71; EHP=1670.120556; normal:17x21,normal:18x31,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10021559,10021561,10049163,10021559,10021561,10049163,10021559,10021561,10049164,10021559,10021561,10049164,10021559,10021561,10049165,10021559,10021561,10049166,10021559,10021561,10049166,10021559,10021561,10049167,10021559,10021561,10049167,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021559,10021559,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560</t>
+          <t>10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021561,10021559,10021559,10021559,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021560,10021559,10021559,10021559,10021559,10021559,10021559,10021559,10021559,10021559</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L29 W4/25; N=77; EHP=694.000000; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x24,normal:18x23,swarm:84x21</t>
+          <t>L29 W4/25; N=77; EHP=2078.989332; normal:17x33,normal:18x23,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10021562,10021565,10049168,10021564,10021562,10021565,10049168,10021564,10021562,10021565,10049169,10021564,10021562,10021565,10049169,10021564,10021562,10021565,10049170,10021566,10021562,10021565,10049170,10021566,10021562,10021565,10049171,10021566,10021562,10021565,10049171,10021566,10021562,10021565,10049172,10021567,10021562,10021565,10049172,10021567,10021562,10021565,10021567,10021562,10021565,10021567,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021563,10021565,10021563,10021565,10021563,10021565,10021563,10021565,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563</t>
+          <t>10021562,10049168,10049168,10021564,10021562,10049168,10049168,10021564,10021562,10049169,10049169,10021564,10021562,10049169,10049169,10021564,10021562,10049170,10049170,10021566,10021562,10049170,10049170,10021566,10021562,10049171,10049171,10021566,10021562,10049171,10049171,10021566,10021562,10049172,10049172,10021567,10021562,10049172,10049172,10021567,10021562,10021565,10021567,10021562,10021565,10021567,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021562,10021565,10021563,10021565,10021563,10021565,10021563,10021565,10021563,10021565,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563,10021563</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L29 W5/25; N=83; EHP=1292.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x19,normal:18x19,medium:83x4,swarm:84x23,medium:108x4,medium:123x4</t>
+          <t>L29 W5/25; N=83; EHP=3641.510317; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x4,normal:17x19,normal:18x19,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10021571,10021577,10021573,10049173,10021576,10021571,10021577,10021573,10049173,10021576,10021571,10021577,10021573,10021568,10021576,10021571,10021577,10021574,10021568,10021576,10021571,10021577,10021574,10021568,10021579,10021571,10021577,10021575,10049174,10021579,10021571,10021577,10021575,10049174,10021579,10021571,10021577,10021575,10021569,10021579,10021571,10021577,10021578,10021569,10021579,10021571,10021577,10021578,10021570,10021580,10021571,10021577,10021570,10021580,10021571,10021577,10021580,10021571,10021577,10021580,10021571,10021577,10021571,10021577,10021571,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021572,10021572,10021572,10021572,10021572,10021572</t>
+          <t>10021571,10049173,10021573,10049173,10021576,10021571,10049173,10021573,10049173,10021576,10021571,10021568,10021573,10021568,10021576,10021571,10021568,10021574,10021568,10021576,10021571,10021568,10021574,10021568,10021579,10021571,10049174,10021575,10049174,10021579,10021571,10049174,10021575,10049174,10021579,10021571,10021569,10021575,10021569,10021579,10021571,10021569,10021578,10021569,10021579,10021571,10021570,10021578,10021570,10021580,10021571,10021570,10021570,10021580,10021571,10021577,10021580,10021571,10021577,10021580,10021571,10021577,10021571,10021577,10021571,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021577,10021572,10021572,10021572,10021572,10021572,10021572,10021572</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L29 W6/25; N=89; EHP=1318.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x5,medium:123x4</t>
+          <t>L29 W6/25; N=89; EHP=3716.790094; air:2x4,air:11x6,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x5,medium:123x4,normal:17x16,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10021584,10021590,10021586,10049175,10021589,10021584,10021590,10021586,10049175,10021589,10021584,10021590,10021586,10021581,10021589,10021584,10021590,10021587,10021581,10021589,10021584,10021590,10021587,10049176,10021589,10021584,10021590,10021587,10049176,10021592,10021584,10021590,10021588,10021582,10021592,10021584,10021590,10021588,10021582,10021592,10021584,10021590,10021591,10021583,10021592,10021584,10021590,10021591,10021583,10021593,10021584,10021590,10021591,10021583,10021593,10021584,10021590,10021593,10021584,10021590,10021593,10021584,10021590,10021593,10021584,10021590,10021584,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021585,10021585,10021585,10021585,10021585,10021585</t>
+          <t>10021584,10049175,10021586,10049175,10021589,10021584,10049175,10021586,10049175,10021589,10021584,10021581,10021586,10021581,10021589,10021584,10021581,10021587,10021581,10021589,10021584,10049176,10021587,10049176,10021589,10021584,10049176,10021587,10049176,10021592,10021584,10021582,10021588,10021582,10021592,10021584,10021582,10021588,10021582,10021592,10021584,10021583,10021591,10021583,10021592,10021584,10021583,10021591,10021583,10021593,10021584,10021583,10021591,10021583,10021593,10021584,10021590,10021593,10021584,10021590,10021593,10021584,10021590,10021593,10021584,10021590,10021584,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021590,10021585,10021585,10021585,10021585,10021585,10021585,10021585</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L29 W7/25; N=95; EHP=1478.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x2,medium:83x5,swarm:84x26,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L29 W7/25; N=95; EHP=4164.332672; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x5,normal:17x16,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10021597,10021603,10021599,10049177,10021602,10021597,10021603,10021599,10049177,10021602,10021597,10021603,10021599,10049177,10021602,10021597,10021603,10021600,10021594,10021602,10021597,10021603,10021600,10021594,10021602,10021597,10021603,10021600,10049178,10021605,10021597,10021603,10021601,10049178,10021605,10021597,10021603,10021601,10049178,10021605,10021597,10021603,10021601,10021595,10021605,10021597,10021603,10021604,10021595,10021605,10021597,10021603,10021604,10021596,10021606,10021597,10021603,10021604,10021596,10021606,10021597,10021603,10021606,10021597,10021603,10021606,10021597,10021603,10021606,10021597,10021603,10021597,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021598,10021598,10021598,10021598,10021598</t>
+          <t>10021597,10049177,10021599,10049177,10021602,10021597,10049177,10021599,10049177,10021602,10021597,10049177,10021599,10049177,10021602,10021597,10021594,10021600,10021594,10021602,10021597,10021594,10021600,10021594,10021602,10021597,10049178,10021600,10049178,10021605,10021597,10049178,10021601,10049178,10021605,10021597,10049178,10021601,10049178,10021605,10021597,10021595,10021601,10021595,10021605,10021597,10021595,10021604,10021595,10021605,10021597,10021596,10021604,10021596,10021606,10021597,10021596,10021604,10021596,10021606,10021597,10021603,10021606,10021597,10021603,10021606,10021597,10021603,10021606,10021597,10021603,10021597,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021603,10021598,10021598,10021598,10021598,10021598,10021598</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L29 W8/25; N=101; EHP=1899.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x17,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L29 W8/25; N=101; EHP=5352.431030; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10021610,10021616,10021612,10049179,10021615,10021610,10021616,10021612,10049179,10021615,10021610,10021616,10021612,10049179,10021615,10021610,10021616,10021613,10021607,10021615,10021610,10021616,10021613,10021607,10021615,10021610,10021616,10021613,10021607,10021618,10021610,10021616,10021614,10049180,10021618,10021610,10021616,10021614,10049180,10021618,10021610,10021616,10021614,10021608,10021618,10021610,10021616,10021617,10021608,10021618,10021610,10021616,10021617,10021608,10021618,10021610,10021616,10021617,10021609,10021619,10021610,10021616,10021609,10021619,10021610,10021616,10021619,10021610,10021616,10021619,10021610,10021616,10021619,10021610,10021616,10021610,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021611,10021611,10021611,10021611,10021611,10021611,10021611</t>
+          <t>10021610,10049179,10021612,10049179,10021615,10021610,10049179,10021612,10049179,10021615,10021610,10049179,10021612,10049179,10021615,10021610,10021607,10021613,10021607,10021615,10021610,10021607,10021613,10021607,10021615,10021610,10021607,10021613,10021607,10021618,10021610,10049180,10021614,10049180,10021618,10021610,10049180,10021614,10049180,10021618,10021610,10021608,10021614,10021608,10021618,10021610,10021608,10021617,10021608,10021618,10021610,10021608,10021617,10021608,10021618,10021610,10021609,10021617,10021609,10021619,10021610,10021609,10021609,10021619,10021610,10021616,10021619,10021610,10021616,10021619,10021610,10021616,10021619,10021610,10021616,10021610,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021616,10021611,10021611,10021611,10021611,10021611,10021611,10021611,10021611</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L29 W9/25; N=107; EHP=2421.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x19,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x6,medium:123x5</t>
+          <t>L29 W9/25; N=107; EHP=6825.442275; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x6,medium:123x5,normal:17x18,normal:18x19,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10021623,10021629,10021625,10049181,10021628,10021623,10021629,10021625,10049181,10021628,10021623,10021629,10021625,10021620,10021628,10021623,10021629,10021626,10021620,10021628,10021623,10021629,10021626,10021620,10021628,10021623,10021629,10021626,10049182,10021628,10021623,10021629,10021627,10049182,10021631,10021623,10021629,10021627,10049182,10021631,10021623,10021629,10021627,10021621,10021631,10021623,10021629,10021627,10021621,10021631,10021623,10021629,10021630,10021621,10021631,10021623,10021629,10021630,10021622,10021632,10021623,10021629,10021630,10021622,10021632,10021623,10021629,10021622,10021632,10021623,10021629,10021632,10021623,10021629,10021632,10021623,10021629,10021623,10021629,10021623,10021629,10021623,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021624,10021624,10021624,10021624,10021624,10021624,10021624</t>
+          <t>10021623,10049181,10021625,10049181,10021628,10021623,10049181,10021625,10049181,10021628,10021623,10021620,10021625,10021620,10021628,10021623,10021620,10021626,10021620,10021628,10021623,10021620,10021626,10021620,10021628,10021623,10049182,10021626,10049182,10021628,10021623,10049182,10021627,10049182,10021631,10021623,10049182,10021627,10049182,10021631,10021623,10021621,10021627,10021621,10021631,10021623,10021621,10021627,10021621,10021631,10021623,10021621,10021630,10021621,10021631,10021623,10021622,10021630,10021622,10021632,10021623,10021622,10021630,10021622,10021632,10021623,10021622,10021622,10021632,10021623,10021629,10021632,10021623,10021629,10021632,10021623,10021629,10021623,10021629,10021623,10021629,10021623,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021629,10021624,10021624,10021624,10021624,10021624,10021624,10021624,10021624</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L29 W10/25; N=113; EHP=4461.000000; air:2x2,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x20,normal:18x19,fast:30x3,fast:58x3,fast:64x4,medium:83x6,swarm:84x31,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L29 W10/25; N=113; EHP=12581.491635; air:2x4,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,medium:83x6,medium:108x5,medium:123x5,normal:17x20,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10021633,10021642,10021635,10049183,10021641,10021636,10021633,10021642,10021635,10049183,10021641,10021637,10021633,10021642,10021635,10049183,10021641,10045318,10021633,10021642,10021635,10049184,10021641,10045319,10021633,10021642,10021638,10049184,10021641,10021640,10021633,10021642,10021638,10049184,10021646,10021640,10021633,10021642,10021638,10049185,10021646,10021643,10021633,10021642,10021639,10049185,10021646,10021643,10021633,10021642,10021639,10049185,10021646,10021644,10021633,10021642,10021639,10049186,10021646,10021644,10021633,10021642,10021645,10049186,10021646,10021648,10021633,10021642,10021645,10049187,10021647,10021633,10021642,10021645,10049187,10021647,10021633,10021642,10021645,10049187,10021647,10021633,10021642,10021647,10021634,10021642,10021647,10021634,10021642,10021647,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021642,10021642,10021642</t>
+          <t>10021633,10049183,10021635,10049183,10021641,10021636,10021633,10049183,10021635,10049183,10021641,10021637,10021633,10049183,10021635,10049183,10021641,10045318,10021633,10049184,10021635,10049184,10021641,10045319,10021633,10049184,10021638,10049184,10021641,10021640,10021633,10049184,10021638,10049184,10021646,10021640,10021633,10049185,10021638,10049185,10021646,10021643,10021633,10049185,10021639,10049185,10021646,10021643,10021633,10049185,10021639,10049185,10021646,10021644,10021633,10049186,10021639,10049186,10021646,10021644,10021633,10049186,10021645,10049186,10021646,10021648,10021633,10049187,10021645,10049187,10021647,10021633,10049187,10021645,10049187,10021647,10021633,10049187,10021645,10049187,10021647,10021633,10021642,10021647,10021634,10021642,10021647,10021634,10021642,10021647,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021634,10021642,10021642,10021642,10021642</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L29 W11/25; N=119; EHP=4551.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x33,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L29 W11/25; N=119; EHP=12808.787152; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x5,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10021652,10021662,10021654,10049188,10021661,10021655,10021652,10021662,10021654,10049188,10021661,10021655,10021652,10021662,10021654,10049188,10021661,10021656,10021652,10021662,10021657,10021649,10021661,10021656,10021652,10021662,10021657,10021649,10021661,10045320,10021652,10021662,10021657,10021649,10021661,10021659,10021652,10021662,10021657,10049189,10021665,10021660,10021652,10021662,10021658,10049189,10021665,10021660,10021652,10021662,10021658,10049189,10021665,10021663,10021652,10021662,10021658,10021650,10021665,10021663,10021652,10021662,10021658,10021650,10021665,10045321,10021652,10021662,10021664,10021650,10021665,10021667,10021652,10021662,10021664,10021651,10021666,10021652,10021662,10021664,10021651,10021666,10021652,10021662,10021664,10021651,10021666,10021653,10021662,10021666,10021653,10021662,10021666,10021653,10021662,10021666,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021662,10021662,10021662,10021662,10021662</t>
+          <t>10021652,10049188,10021654,10049188,10021661,10021655,10021652,10049188,10021654,10049188,10021661,10021655,10021652,10049188,10021654,10049188,10021661,10021656,10021652,10021649,10021657,10021649,10021661,10021656,10021652,10021649,10021657,10021649,10021661,10045320,10021652,10021649,10021657,10021649,10021661,10021659,10021652,10049189,10021657,10049189,10021665,10021660,10021652,10049189,10021658,10049189,10021665,10021660,10021652,10049189,10021658,10049189,10021665,10021663,10021652,10021650,10021658,10021650,10021665,10021663,10021652,10021650,10021658,10021650,10021665,10045321,10021652,10021650,10021664,10021650,10021665,10021667,10021652,10021651,10021664,10021651,10021666,10021652,10021651,10021664,10021651,10021666,10021652,10021651,10021664,10021651,10021666,10021653,10021662,10021666,10021653,10021662,10021666,10021653,10021662,10021666,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021653,10021662,10021662,10021662,10021662,10021662,10021662</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L29 W12/25; N=125; EHP=4708.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L29 W12/25; N=125; EHP=13253.285399; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10021671,10021681,10021673,10049190,10021680,10021674,10021671,10021681,10021673,10049190,10021680,10021674,10021671,10021681,10021673,10049190,10021680,10021675,10021671,10021681,10021673,10021668,10021680,10021675,10021671,10021681,10021676,10021668,10021680,10021678,10021671,10021681,10021676,10021668,10021680,10021679,10021671,10021681,10021676,10049191,10021680,10021679,10021671,10021681,10021676,10049191,10021685,10045322,10021671,10021681,10021677,10049191,10021685,10021682,10021671,10021681,10021677,10049191,10021685,10021682,10021671,10021681,10021677,10021669,10021685,10021683,10021671,10021681,10021677,10021669,10021685,10021687,10021671,10021681,10021684,10021669,10021685,10021687,10021671,10021681,10021684,10021670,10021686,10021671,10021681,10021684,10021670,10021686,10021671,10021681,10021670,10021686,10021672,10021681,10021686,10021672,10021681,10021686,10021672,10021681,10021686,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021681,10021681,10021681,10021681</t>
+          <t>10021671,10049190,10021673,10049190,10021680,10021674,10021671,10049190,10021673,10049190,10021680,10021674,10021671,10049190,10021673,10049190,10021680,10021675,10021671,10021668,10021673,10021668,10021680,10021675,10021671,10021668,10021676,10021668,10021680,10021678,10021671,10021668,10021676,10021668,10021680,10021679,10021671,10049191,10021676,10049191,10021680,10021679,10021671,10049191,10021676,10049191,10021685,10045322,10021671,10049191,10021677,10049191,10021685,10021682,10021671,10049191,10021677,10049191,10021685,10021682,10021671,10021669,10021677,10021669,10021685,10021683,10021671,10021669,10021677,10021669,10021685,10021687,10021671,10021669,10021684,10021669,10021685,10021687,10021671,10021670,10021684,10021670,10021686,10021671,10021670,10021684,10021670,10021686,10021671,10021670,10021670,10021686,10021672,10021681,10021686,10021672,10021681,10021686,10021672,10021681,10021686,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021672,10021681,10021681,10021681,10021681,10021681</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L29 W13/25; N=131; EHP=5742.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x36,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L29 W13/25; N=131; EHP=16166.253997; air:2x6,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10021691,10021702,10021693,10049192,10021701,10021694,10021691,10021702,10021693,10049192,10021701,10021694,10021691,10021702,10021693,10049192,10021701,10021695,10021691,10021702,10021693,10049192,10021701,10021695,10021691,10021702,10021696,10021688,10021701,10021698,10021691,10021702,10021696,10021688,10021701,10021698,10021691,10021702,10021696,10021688,10021705,10021699,10021691,10021702,10021696,10049193,10021705,10021699,10021691,10021702,10021697,10049193,10021705,10021700,10021691,10021702,10021697,10049193,10021705,10045323,10021691,10021702,10021697,10021689,10021705,10021703,10021691,10021702,10021697,10021689,10021705,10021707,10021691,10021702,10021704,10021689,10021705,10021707,10021691,10021702,10021704,10021690,10021706,10021691,10021702,10021704,10021690,10021706,10021691,10021702,10021704,10021690,10021706,10021691,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021702,10021702,10021702,10021702</t>
+          <t>10021691,10049192,10021693,10049192,10021701,10021694,10021691,10049192,10021693,10049192,10021701,10021694,10021691,10049192,10021693,10049192,10021701,10021695,10021691,10049192,10021693,10049192,10021701,10021695,10021691,10021688,10021696,10021688,10021701,10021698,10021691,10021688,10021696,10021688,10021701,10021698,10021691,10021688,10021696,10021688,10021705,10021699,10021691,10049193,10021696,10049193,10021705,10021699,10021691,10049193,10021697,10049193,10021705,10021700,10021691,10049193,10021697,10049193,10021705,10045323,10021691,10021689,10021697,10021689,10021705,10021703,10021691,10021689,10021697,10021689,10021705,10021707,10021691,10021689,10021704,10021689,10021705,10021707,10021691,10021690,10021704,10021690,10021706,10021691,10021690,10021704,10021690,10021706,10021691,10021690,10021704,10021690,10021706,10021691,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021706,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021692,10021702,10021702,10021702,10021702,10021702</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L29 W14/25; N=137; EHP=6925.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x38,heavy:86x1,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L29 W14/25; N=137; EHP=19487.602758; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10021711,10021722,10021713,10049194,10021721,10045324,10021717,10021711,10021722,10021713,10049194,10021721,10021714,10021711,10021722,10021713,10049194,10021721,10021714,10021711,10021722,10021713,10021708,10021721,10021718,10021711,10021722,10021713,10021708,10021721,10021718,10021711,10021722,10021715,10021708,10021721,10021719,10021711,10021722,10021715,10021708,10021721,10021719,10021711,10021722,10021715,10049195,10021726,10021720,10021711,10021722,10021715,10049195,10021726,10021720,10021711,10021722,10021716,10049195,10021726,10021723,10021711,10021722,10021716,10021709,10021726,10021724,10021711,10021722,10021716,10021709,10021726,10021724,10021711,10021722,10021716,10021709,10021726,10021728,10021711,10021722,10021725,10021709,10021726,10021728,10021711,10021722,10021725,10021710,10021727,10021711,10021722,10021725,10021710,10021727,10021712,10021722,10021725,10021710,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021722,10021722,10021722,10021722,10021722,10021722,10021722</t>
+          <t>10021711,10049194,10021713,10049194,10021721,10045324,10021717,10021711,10049194,10021713,10049194,10021721,10021714,10021711,10049194,10021713,10049194,10021721,10021714,10021711,10021708,10021713,10021708,10021721,10021718,10021711,10021708,10021713,10021708,10021721,10021718,10021711,10021708,10021715,10021708,10021721,10021719,10021711,10021708,10021715,10021708,10021721,10021719,10021711,10049195,10021715,10049195,10021726,10021720,10021711,10049195,10021715,10049195,10021726,10021720,10021711,10049195,10021716,10049195,10021726,10021723,10021711,10021709,10021716,10021709,10021726,10021724,10021711,10021709,10021716,10021709,10021726,10021724,10021711,10021709,10021716,10021709,10021726,10021728,10021711,10021709,10021725,10021709,10021726,10021728,10021711,10021710,10021725,10021710,10021727,10021711,10021710,10021725,10021710,10021727,10021712,10021710,10021725,10021710,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021727,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021712,10021722,10021722,10021722,10021722,10021722,10021722,10021722,10021722</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L29 W15/25; N=143; EHP=12084.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x17,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L29 W15/25; N=143; EHP=34001.990260; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x16,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10021729,10021739,10021731,10049196,10021738,10021732,10021729,10021739,10021731,10049196,10021738,10045325,10021729,10021739,10021731,10049196,10021738,10021735,10021729,10021739,10021731,10049197,10021738,10021735,10021729,10021739,10021733,10049197,10021738,10021736,10021729,10021739,10021733,10049197,10021738,10021736,10021729,10021739,10021733,10049197,10021738,10021737,10021729,10021739,10021733,10049198,10021738,10021737,10021729,10021739,10021734,10049198,10021743,10021740,10021729,10021739,10021734,10049198,10021743,10021740,10021729,10021739,10021734,10049198,10021743,10021741,10021729,10021739,10021734,10049199,10021743,10021741,10021729,10021739,10021742,10049199,10021743,10021745,10021729,10021739,10021742,10049199,10021743,10021745,10021729,10021739,10021742,10049200,10021743,10021729,10021739,10021742,10049200,10021744,10021729,10021739,10021742,10049200,10021744,10021729,10021739,10049200,10021744,10021729,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021739,10021739,10021739,10021739</t>
+          <t>10021729,10049196,10021731,10049196,10021738,10021732,10021729,10049196,10021731,10049196,10021738,10045325,10021729,10049196,10021731,10049196,10021738,10021735,10021729,10049197,10021731,10049197,10021738,10021735,10021729,10049197,10021733,10049197,10021738,10021736,10021729,10049197,10021733,10049197,10021738,10021736,10021729,10049197,10021733,10049197,10021738,10021737,10021729,10049198,10021733,10049198,10021738,10021737,10021729,10049198,10021734,10049198,10021743,10021740,10021729,10049198,10021734,10049198,10021743,10021740,10021729,10049198,10021734,10049198,10021743,10021741,10021729,10049199,10021734,10049199,10021743,10021741,10021729,10049199,10021742,10049199,10021743,10021745,10021729,10049199,10021742,10049199,10021743,10021745,10021729,10049200,10021742,10049200,10021743,10021729,10049200,10021742,10049200,10021744,10021729,10049200,10021742,10049200,10021744,10021729,10049200,10049200,10021744,10021729,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021744,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021730,10021739,10021739,10021739,10021739,10021739</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L29 W16/25; N=149; EHP=12326.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x18,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L29 W16/25; N=149; EHP=34700.189558; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x19,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10021749,10021760,10021751,10049201,10021759,10021752,10021749,10021760,10021751,10049201,10021759,10021752,10021749,10021760,10021751,10049201,10021759,10021753,10021749,10021760,10021751,10049201,10021759,10021753,10021749,10021760,10021754,10021746,10021759,10021756,10021749,10021760,10021754,10021746,10021759,10021756,10021749,10021760,10021754,10021746,10021759,10021757,10021749,10021760,10021754,10049202,10021764,10021757,10021749,10021760,10021754,10049202,10021764,10021758,10021749,10021760,10021755,10049202,10021764,10021758,10021749,10021760,10021755,10049202,10021764,10021761,10021749,10021760,10021755,10021747,10021764,10021761,10021749,10021760,10021755,10021747,10021764,10021762,10021749,10021760,10021755,10021747,10021764,10021762,10021749,10021760,10021763,10021747,10021764,10045326,10021749,10021760,10021763,10021748,10021765,10021749,10021760,10021763,10021748,10021765,10021749,10021760,10021763,10021748,10021765,10021750,10021760,10021748,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021760,10021760,10021760,10021760,10021760,10021760</t>
+          <t>10021749,10049201,10021751,10049201,10021759,10021752,10021749,10049201,10021751,10049201,10021759,10021752,10021749,10049201,10021751,10049201,10021759,10021753,10021749,10049201,10021751,10049201,10021759,10021753,10021749,10021746,10021754,10021746,10021759,10021756,10021749,10021746,10021754,10021746,10021759,10021756,10021749,10021746,10021754,10021746,10021759,10021757,10021749,10049202,10021754,10049202,10021764,10021757,10021749,10049202,10021754,10049202,10021764,10021758,10021749,10049202,10021755,10049202,10021764,10021758,10021749,10049202,10021755,10049202,10021764,10021761,10021749,10021747,10021755,10021747,10021764,10021761,10021749,10021747,10021755,10021747,10021764,10021762,10021749,10021747,10021755,10021747,10021764,10021762,10021749,10021747,10021763,10021747,10021764,10045326,10021749,10021748,10021763,10021748,10021765,10021749,10021748,10021763,10021748,10021765,10021749,10021748,10021763,10021748,10021765,10021750,10021748,10021748,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021765,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021750,10021760,10021760,10021760,10021760,10021760,10021760,10021760</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L29 W17/25; N=155; EHP=12573.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x4,normal:17x18,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x1</t>
+          <t>L29 W17/25; N=155; EHP=35400.811887; air:2x8,air:11x6,air:12x8,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x8,medium:123x8,normal:17x18,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10021769,10021780,10021771,10049203,10021779,10021772,10021769,10021780,10021771,10049203,10021779,10021772,10021769,10021780,10021771,10049203,10021779,10021773,10021769,10021780,10021771,10049203,10021779,10021773,10021769,10021780,10021771,10021766,10021779,10021776,10021769,10021780,10021774,10021766,10021779,10021776,10021769,10021780,10021774,10021766,10021779,10021777,10021769,10021780,10021774,10021766,10021779,10021777,10021769,10021780,10021774,10049204,10021784,10021778,10021769,10021780,10021775,10049204,10021784,10021778,10021769,10021780,10021775,10049204,10021784,10021781,10021769,10021780,10021775,10049204,10021784,10021781,10021769,10021780,10021775,10021767,10021784,10021782,10021769,10021780,10021775,10021767,10021784,10021782,10021769,10021780,10021783,10021767,10021784,10021786,10021769,10021780,10021783,10021767,10021784,10021786,10021769,10021780,10021783,10021768,10021785,10021769,10021780,10021783,10021768,10021785,10021769,10021780,10021783,10021768,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021780,10021780,10021780,10021780,10021780,10021780,10021780</t>
+          <t>10021769,10049203,10021771,10049203,10021779,10021772,10021769,10049203,10021771,10049203,10021779,10021772,10021769,10049203,10021771,10049203,10021779,10021773,10021769,10049203,10021771,10049203,10021779,10021773,10021769,10021766,10021771,10021766,10021779,10021776,10021769,10021766,10021774,10021766,10021779,10021776,10021769,10021766,10021774,10021766,10021779,10021777,10021769,10021766,10021774,10021766,10021779,10021777,10021769,10049204,10021774,10049204,10021784,10021778,10021769,10049204,10021775,10049204,10021784,10021778,10021769,10049204,10021775,10049204,10021784,10021781,10021769,10049204,10021775,10049204,10021784,10021781,10021769,10021767,10021775,10021767,10021784,10021782,10021769,10021767,10021775,10021767,10021784,10021782,10021769,10021767,10021783,10021767,10021784,10021786,10021769,10021767,10021783,10021767,10021784,10021786,10021769,10021768,10021783,10021768,10021785,10021769,10021768,10021783,10021768,10021785,10021769,10021768,10021783,10021768,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021785,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021770,10021780,10021780,10021780,10021780,10021780,10021780,10021780,10021780</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L29 W18/25; N=161; EHP=13433.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L29 W18/25; N=161; EHP=37803.717410; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10021790,10021801,10021792,10049205,10021800,10021793,10021790,10021801,10021792,10049205,10021800,10021793,10021790,10021801,10021792,10049205,10021800,10021794,10021790,10021801,10021792,10049205,10021800,10021794,10021790,10021801,10021792,10021787,10021800,10021797,10021790,10021801,10021795,10021787,10021800,10021797,10021790,10021801,10021795,10021787,10021800,10021798,10021790,10021801,10021795,10021787,10021800,10021798,10021790,10021801,10021795,10049206,10021800,10021799,10021790,10021801,10021795,10049206,10021805,10021799,10021790,10021801,10021796,10049206,10021805,10021802,10021790,10021801,10021796,10049206,10021805,10021802,10021790,10021801,10021796,10021788,10021805,10021803,10021790,10021801,10021796,10021788,10021805,10021803,10021790,10021801,10021796,10021788,10021805,10021807,10021790,10021801,10021804,10021788,10021805,10021807,10021790,10021801,10021804,10021789,10021805,10021790,10021801,10021804,10021789,10021806,10021790,10021801,10021804,10021789,10021806,10021790,10021801,10021804,10021789,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021801,10021801,10021801,10021801,10021801,10021801</t>
+          <t>10021790,10049205,10021792,10049205,10021800,10021793,10021790,10049205,10021792,10049205,10021800,10021793,10021790,10049205,10021792,10049205,10021800,10021794,10021790,10049205,10021792,10049205,10021800,10021794,10021790,10021787,10021792,10021787,10021800,10021797,10021790,10021787,10021795,10021787,10021800,10021797,10021790,10021787,10021795,10021787,10021800,10021798,10021790,10021787,10021795,10021787,10021800,10021798,10021790,10049206,10021795,10049206,10021800,10021799,10021790,10049206,10021795,10049206,10021805,10021799,10021790,10049206,10021796,10049206,10021805,10021802,10021790,10049206,10021796,10049206,10021805,10021802,10021790,10021788,10021796,10021788,10021805,10021803,10021790,10021788,10021796,10021788,10021805,10021803,10021790,10021788,10021796,10021788,10021805,10021807,10021790,10021788,10021804,10021788,10021805,10021807,10021790,10021789,10021804,10021789,10021805,10021790,10021789,10021804,10021789,10021806,10021790,10021789,10021804,10021789,10021806,10021790,10021789,10021804,10021789,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021806,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021791,10021801,10021801,10021801,10021801,10021801,10021801,10021801</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L29 W19/25; N=167; EHP=15559.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L29 W19/25; N=167; EHP=43795.795764; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10021811,10021823,10021813,10049207,10021822,10021814,10021818,10021811,10021823,10021813,10049207,10021822,10021814,10021811,10021823,10021813,10049207,10021822,10021815,10021811,10021823,10021813,10049207,10021822,10021815,10021811,10021823,10021813,10021808,10021822,10021819,10021811,10021823,10021816,10021808,10021822,10021819,10021811,10021823,10021816,10021808,10021822,10021820,10021811,10021823,10021816,10021808,10021822,10021820,10021811,10021823,10021816,10049208,10021827,10021821,10021811,10021823,10021816,10049208,10021827,10021821,10021811,10021823,10021817,10049208,10021827,10021821,10021811,10021823,10021817,10049208,10021827,10021824,10021811,10021823,10021817,10021809,10021827,10021824,10021811,10021823,10021817,10021809,10021827,10021825,10021811,10021823,10021817,10021809,10021827,10021825,10021811,10021823,10021826,10021809,10021827,10021829,10021811,10021823,10021826,10021809,10021828,10021829,10021811,10021823,10021826,10021810,10021828,10021811,10021823,10021826,10021810,10021828,10021811,10021823,10021826,10021810,10021828,10021811,10021823,10021810,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021823,10021823,10021823,10021823,10021823,10021823,10021823</t>
+          <t>10021811,10049207,10021813,10049207,10021822,10021814,10021818,10021811,10049207,10021813,10049207,10021822,10021814,10021811,10049207,10021813,10049207,10021822,10021815,10021811,10049207,10021813,10049207,10021822,10021815,10021811,10021808,10021813,10021808,10021822,10021819,10021811,10021808,10021816,10021808,10021822,10021819,10021811,10021808,10021816,10021808,10021822,10021820,10021811,10021808,10021816,10021808,10021822,10021820,10021811,10049208,10021816,10049208,10021827,10021821,10021811,10049208,10021816,10049208,10021827,10021821,10021811,10049208,10021817,10049208,10021827,10021821,10021811,10049208,10021817,10049208,10021827,10021824,10021811,10021809,10021817,10021809,10021827,10021824,10021811,10021809,10021817,10021809,10021827,10021825,10021811,10021809,10021817,10021809,10021827,10021825,10021811,10021809,10021826,10021809,10021827,10021829,10021811,10021809,10021826,10021809,10021828,10021829,10021811,10021810,10021826,10021810,10021828,10021811,10021810,10021826,10021810,10021828,10021811,10021810,10021826,10021810,10021828,10021811,10021810,10021810,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021828,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021812,10021823,10021823,10021823,10021823,10021823,10021823,10021823,10021823</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L29 W20/25; N=173; EHP=26111.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x8,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L29 W20/25; N=173; EHP=73492.898922; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10021833,10021844,10021835,10049209,10021843,10021836,10021833,10021844,10021835,10049209,10021843,10021836,10021833,10021844,10021835,10049209,10021843,10021837,10021833,10021844,10021835,10049209,10021843,10021837,10021833,10021844,10021835,10021830,10021843,10021840,10021833,10021844,10021838,10021830,10021843,10021840,10021833,10021844,10021838,10021830,10021843,10021841,10021833,10021844,10021838,10021830,10021843,10021841,10021833,10021844,10021838,10021830,10021843,10021842,10021833,10021844,10021838,10049210,10021848,10021842,10021833,10021844,10021838,10049210,10021848,10021845,10021833,10021844,10021839,10049210,10021848,10021845,10021833,10021844,10021839,10049210,10021848,10021845,10021833,10021844,10021839,10021831,10021848,10021846,10021833,10021844,10021839,10021831,10021848,10021846,10021833,10021844,10021839,10021831,10021848,10021850,10021833,10021844,10021847,10021831,10021848,10021850,10021833,10021844,10021847,10021832,10021848,10021833,10021844,10021847,10021832,10021849,10021833,10021844,10021847,10021832,10021849,10021833,10021844,10021847,10021832,10021849,10021833,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021844,10021844,10021844,10021844,10021844,10021844</t>
+          <t>10021833,10049209,10021835,10049209,10021843,10021836,10021833,10049209,10021835,10049209,10021843,10021836,10021833,10049209,10021835,10049209,10021843,10021837,10021833,10049209,10021835,10049209,10021843,10021837,10021833,10021830,10021835,10021830,10021843,10021840,10021833,10021830,10021838,10021830,10021843,10021840,10021833,10021830,10021838,10021830,10021843,10021841,10021833,10021830,10021838,10021830,10021843,10021841,10021833,10021830,10021838,10021830,10021843,10021842,10021833,10049210,10021838,10049210,10021848,10021842,10021833,10049210,10021838,10049210,10021848,10021845,10021833,10049210,10021839,10049210,10021848,10021845,10021833,10049210,10021839,10049210,10021848,10021845,10021833,10021831,10021839,10021831,10021848,10021846,10021833,10021831,10021839,10021831,10021848,10021846,10021833,10021831,10021839,10021831,10021848,10021850,10021833,10021831,10021847,10021831,10021848,10021850,10021833,10021832,10021847,10021832,10021848,10021833,10021832,10021847,10021832,10021849,10021833,10021832,10021847,10021832,10021849,10021833,10021832,10021847,10021832,10021849,10021833,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021849,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021834,10021844,10021844,10021844,10021844,10021844,10021844,10021844</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L29 W21/25; N=179; EHP=26634.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L29 W21/25; N=179; EHP=74955.566006; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10021854,10021865,10021856,10049211,10021864,10021857,10021854,10021865,10021856,10049211,10021864,10021857,10021854,10021865,10021856,10049211,10021864,10021857,10021854,10021865,10021856,10049211,10021864,10021858,10021854,10021865,10021856,10021851,10021864,10021858,10021854,10021865,10021856,10021851,10021864,10021858,10021854,10021865,10021859,10021851,10021864,10021861,10021854,10021865,10021859,10021851,10021864,10021861,10021854,10021865,10021859,10049212,10021864,10021862,10021854,10021865,10021859,10049212,10021869,10021862,10021854,10021865,10021859,10049212,10021869,10021863,10021854,10021865,10021860,10049212,10021869,10021863,10021854,10021865,10021860,10049212,10021869,10021866,10021854,10021865,10021860,10021852,10021869,10021866,10021854,10021865,10021860,10021852,10021869,10021867,10021854,10021865,10021860,10021852,10021869,10021867,10021854,10021865,10021860,10021852,10021869,10021871,10021854,10021865,10021868,10021853,10021869,10021871,10021854,10021865,10021868,10021853,10021870,10021854,10021865,10021868,10021853,10021870,10021854,10021865,10021868,10021853,10021870,10021854,10021865,10021868,10021853,10021870,10021854,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021865,10021865,10021865,10021865,10021865,10021865</t>
+          <t>10021854,10049211,10021856,10049211,10021864,10021857,10021854,10049211,10021856,10049211,10021864,10021857,10021854,10049211,10021856,10049211,10021864,10021857,10021854,10049211,10021856,10049211,10021864,10021858,10021854,10021851,10021856,10021851,10021864,10021858,10021854,10021851,10021856,10021851,10021864,10021858,10021854,10021851,10021859,10021851,10021864,10021861,10021854,10021851,10021859,10021851,10021864,10021861,10021854,10049212,10021859,10049212,10021864,10021862,10021854,10049212,10021859,10049212,10021869,10021862,10021854,10049212,10021859,10049212,10021869,10021863,10021854,10049212,10021860,10049212,10021869,10021863,10021854,10049212,10021860,10049212,10021869,10021866,10021854,10021852,10021860,10021852,10021869,10021866,10021854,10021852,10021860,10021852,10021869,10021867,10021854,10021852,10021860,10021852,10021869,10021867,10021854,10021852,10021860,10021852,10021869,10021871,10021854,10021853,10021868,10021853,10021869,10021871,10021854,10021853,10021868,10021853,10021870,10021854,10021853,10021868,10021853,10021870,10021854,10021853,10021868,10021853,10021870,10021854,10021853,10021868,10021853,10021870,10021854,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021870,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021855,10021865,10021865,10021865,10021865,10021865,10021865,10021865</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L29 W22/25; N=185; EHP=27167.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x23,normal:18x22,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L29 W22/25; N=185; EHP=76464.390669; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x23,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10021875,10021886,10021877,10049213,10021885,10021878,10021875,10021886,10021877,10049213,10021885,10021878,10021875,10021886,10021877,10049213,10021885,10021879,10021875,10021886,10021877,10049213,10021885,10021879,10021875,10021886,10021877,10049213,10021885,10021879,10021875,10021886,10021877,10021872,10021885,10021882,10021875,10021886,10021880,10021872,10021885,10021882,10021875,10021886,10021880,10021872,10021885,10021883,10021875,10021886,10021880,10021872,10021885,10021883,10021875,10021886,10021880,10049214,10021890,10021883,10021875,10021886,10021880,10049214,10021890,10021884,10021875,10021886,10021881,10049214,10021890,10021884,10021875,10021886,10021881,10049214,10021890,10021887,10021875,10021886,10021881,10049214,10021890,10021887,10021875,10021886,10021881,10021873,10021890,10021888,10021875,10021886,10021881,10021873,10021890,10021888,10021875,10021886,10021889,10021873,10021890,10021892,10021875,10021886,10021889,10021873,10021890,10021892,10021875,10021886,10021889,10021873,10021891,10021892,10021875,10021886,10021889,10021874,10021891,10021875,10021886,10021889,10021874,10021891,10021875,10021886,10021889,10021874,10021891,10021875,10021886,10021874,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021886,10021886,10021886,10021886,10021886,10021886,10021886</t>
+          <t>10021875,10049213,10021877,10049213,10021885,10021878,10021875,10049213,10021877,10049213,10021885,10021878,10021875,10049213,10021877,10049213,10021885,10021879,10021875,10049213,10021877,10049213,10021885,10021879,10021875,10049213,10021877,10049213,10021885,10021879,10021875,10021872,10021877,10021872,10021885,10021882,10021875,10021872,10021880,10021872,10021885,10021882,10021875,10021872,10021880,10021872,10021885,10021883,10021875,10021872,10021880,10021872,10021885,10021883,10021875,10049214,10021880,10049214,10021890,10021883,10021875,10049214,10021880,10049214,10021890,10021884,10021875,10049214,10021881,10049214,10021890,10021884,10021875,10049214,10021881,10049214,10021890,10021887,10021875,10049214,10021881,10049214,10021890,10021887,10021875,10021873,10021881,10021873,10021890,10021888,10021875,10021873,10021881,10021873,10021890,10021888,10021875,10021873,10021889,10021873,10021890,10021892,10021875,10021873,10021889,10021873,10021890,10021892,10021875,10021873,10021889,10021873,10021891,10021892,10021875,10021874,10021889,10021874,10021891,10021875,10021874,10021889,10021874,10021891,10021875,10021874,10021889,10021874,10021891,10021875,10021874,10021874,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021891,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021876,10021886,10021886,10021886,10021886,10021886,10021886,10021886,10021886</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L29 W23/25; N=191; EHP=27711.000000; air:2x5,air:11x4,air:12x5,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x53,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x3</t>
+          <t>L29 W23/25; N=191; EHP=78004.802554; air:2x10,air:11x8,air:12x10,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x10,normal:17x23,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10021896,10021907,10021898,10049215,10021906,10021899,10021896,10021907,10021898,10049215,10021906,10021899,10021896,10021907,10021898,10049215,10021906,10021900,10021896,10021907,10021898,10049215,10021906,10021900,10021896,10021907,10021898,10049215,10021906,10021903,10021896,10021907,10021901,10021893,10021906,10021903,10021896,10021907,10021901,10021893,10021906,10021903,10021896,10021907,10021901,10021893,10021906,10021904,10021896,10021907,10021901,10021893,10021906,10021904,10021896,10021907,10021901,10021893,10021906,10021904,10021896,10021907,10021901,10049216,10021911,10021905,10021896,10021907,10021902,10049216,10021911,10021905,10021896,10021907,10021902,10049216,10021911,10021908,10021896,10021907,10021902,10049216,10021911,10021908,10021896,10021907,10021902,10021894,10021911,10021909,10021896,10021907,10021902,10021894,10021911,10021909,10021896,10021907,10021902,10021894,10021911,10021913,10021896,10021907,10021910,10021894,10021911,10021913,10021896,10021907,10021910,10021894,10021911,10021913,10021896,10021907,10021910,10021895,10021911,10021896,10021907,10021910,10021895,10021912,10021896,10021907,10021910,10021895,10021912,10021896,10021907,10021910,10021895,10021912,10021896,10021907,10021895,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021907,10021907,10021907,10021907,10021907,10021907,10021907,10021907</t>
+          <t>10021896,10049215,10021898,10049215,10021906,10021899,10021896,10049215,10021898,10049215,10021906,10021899,10021896,10049215,10021898,10049215,10021906,10021900,10021896,10049215,10021898,10049215,10021906,10021900,10021896,10049215,10021898,10049215,10021906,10021903,10021896,10021893,10021901,10021893,10021906,10021903,10021896,10021893,10021901,10021893,10021906,10021903,10021896,10021893,10021901,10021893,10021906,10021904,10021896,10021893,10021901,10021893,10021906,10021904,10021896,10021893,10021901,10021893,10021906,10021904,10021896,10049216,10021901,10049216,10021911,10021905,10021896,10049216,10021902,10049216,10021911,10021905,10021896,10049216,10021902,10049216,10021911,10021908,10021896,10049216,10021902,10049216,10021911,10021908,10021896,10021894,10021902,10021894,10021911,10021909,10021896,10021894,10021902,10021894,10021911,10021909,10021896,10021894,10021902,10021894,10021911,10021913,10021896,10021894,10021910,10021894,10021911,10021913,10021896,10021894,10021910,10021894,10021911,10021913,10021896,10021895,10021910,10021895,10021911,10021896,10021895,10021910,10021895,10021912,10021896,10021895,10021910,10021895,10021912,10021896,10021895,10021910,10021895,10021912,10021896,10021895,10021895,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021912,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021897,10021907,10021907,10021907,10021907,10021907,10021907,10021907,10021907,10021907</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L29 W24/25; N=197; EHP=29674.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x24,normal:18x23,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x55,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x9,heavy:127x3</t>
+          <t>L29 W24/25; N=197; EHP=83546.184759; air:2x10,air:11x10,air:12x8,air:13x10,air:14x10,fast:30x5,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x10,medium:123x9,normal:17x24,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10021917,10021928,10021919,10049217,10021927,10021920,10021935,10021917,10021928,10021919,10049217,10021927,10021920,10021917,10021928,10021919,10049217,10021927,10021921,10021917,10021928,10021919,10049217,10021927,10021921,10021917,10021928,10021919,10021914,10021927,10021924,10021917,10021928,10021919,10021914,10021927,10021924,10021917,10021928,10021922,10021914,10021927,10021924,10021917,10021928,10021922,10021914,10021927,10021925,10021917,10021928,10021922,10021914,10021927,10021925,10021917,10021928,10021922,10049218,10021927,10021925,10021917,10021928,10021922,10049218,10021932,10021926,10021917,10021928,10021922,10049218,10021932,10021926,10021917,10021928,10021923,10049218,10021932,10021926,10021917,10021928,10021923,10049218,10021932,10021929,10021917,10021928,10021923,10021915,10021932,10021929,10021917,10021928,10021923,10021915,10021932,10021930,10021917,10021928,10021923,10021915,10021932,10021930,10021917,10021928,10021923,10021915,10021932,10021930,10021917,10021928,10021931,10021915,10021932,10021934,10021917,10021928,10021931,10021916,10021932,10021934,10021917,10021928,10021931,10021916,10021933,10021917,10021928,10021931,10021916,10021933,10021917,10021928,10021931,10021916,10021933,10021917,10021928,10021931,10021916,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021928,10021928,10021928,10021928,10021928,10021928,10021928,10021928</t>
+          <t>10021917,10049217,10021919,10049217,10021927,10021920,10021935,10021917,10049217,10021919,10049217,10021927,10021920,10021917,10049217,10021919,10049217,10021927,10021921,10021917,10049217,10021919,10049217,10021927,10021921,10021917,10021914,10021919,10021914,10021927,10021924,10021917,10021914,10021919,10021914,10021927,10021924,10021917,10021914,10021922,10021914,10021927,10021924,10021917,10021914,10021922,10021914,10021927,10021925,10021917,10021914,10021922,10021914,10021927,10021925,10021917,10049218,10021922,10049218,10021927,10021925,10021917,10049218,10021922,10049218,10021932,10021926,10021917,10049218,10021922,10049218,10021932,10021926,10021917,10049218,10021923,10049218,10021932,10021926,10021917,10049218,10021923,10049218,10021932,10021929,10021917,10021915,10021923,10021915,10021932,10021929,10021917,10021915,10021923,10021915,10021932,10021930,10021917,10021915,10021923,10021915,10021932,10021930,10021917,10021915,10021923,10021915,10021932,10021930,10021917,10021915,10021931,10021915,10021932,10021934,10021917,10021916,10021931,10021916,10021932,10021934,10021917,10021916,10021931,10021916,10021933,10021917,10021916,10021931,10021916,10021933,10021917,10021916,10021931,10021916,10021933,10021917,10021916,10021931,10021916,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021933,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021918,10021928,10021928,10021928,10021928,10021928,10021928,10021928,10021928,10021928</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L29 W25/25; N=203; EHP=59222.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x24,normal:18x24,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x3,medium:83x10,swarm:84x56,heavy:86x2,heavy:88x3,fast:98x6,medium:108x10,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L29 W25/25; N=203; EHP=166635.203942; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x10,medium:108x10,medium:123x10,normal:17x24,normal:18x24,swarm:84x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L29/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L29/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>224</v>
+        <v>370</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>203</v>
+        <v>390</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>189</v>
+        <v>300</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>168</v>
+        <v>310</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>161</v>
+        <v>390</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>154</v>
+        <v>320</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>147</v>
+        <v>340</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
